--- a/ops/sheet-data/EnglishLab-Sheet-TaiKhoan.xlsx
+++ b/ops/sheet-data/EnglishLab-Sheet-TaiKhoan.xlsx
@@ -1,7 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EngLishLab\EnglishLab\ops\sheet-data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8561C796-6683-4D08-B9C3-ACAE5FF9C950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Huong_dan" sheetId="1" r:id="rId1"/>
     <sheet name="Quan_tri" sheetId="2" r:id="rId2"/>
@@ -12,37 +22,21 @@
     <sheet name="Tat_ca" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2">Giao_vien!$A$1:$G$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4">Hoc_vien_sheet!$A$1:$F$300</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3">Hoc_vien_showcase!$A$1:$G$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">Huong_dan!$A$1:$B$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5">Lop_hoc!$A$1:$L$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1">Quan_tri!$A$1:$F$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2">Giao_vien!$A$1:$G$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3">Hoc_vien_showcase!$A$1:$G$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4">Hoc_vien_sheet!$A$1:$F$300</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5">Lop_hoc!$A$1:$L$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6">Tat_ca!$A$1:$F$326</definedName>
   </definedNames>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3510,14 +3504,19 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3540,17 +3539,28 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -3875,14 +3885,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.83203125" customWidth="1"/>
-    <col min="2" max="2" width="62.83203125" customWidth="1"/>
+    <col min="1" max="1" width="33.875" customWidth="1"/>
+    <col min="2" max="2" width="62.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3890,7 +3901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -3898,7 +3909,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -3906,7 +3917,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -3914,7 +3925,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -3922,7 +3933,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -3930,7 +3941,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -3938,7 +3949,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -3946,7 +3957,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -3954,7 +3965,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -3962,7 +3973,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -3970,15 +3981,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>22</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -3987,26 +3998,31 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B13"/>
+  <autoFilter ref="A1:B13" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <hyperlinks>
+    <hyperlink ref="B12" r:id="rId1" xr:uid="{8FC31AD9-BD85-4848-969B-9B58E903E770}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B13"/>
+    <ignoredError sqref="A1:B11 A13:B13 A12" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="17.83203125" customWidth="1"/>
-    <col min="3" max="3" width="19.83203125" customWidth="1"/>
-    <col min="4" max="4" width="33.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="31.83203125" customWidth="1"/>
+    <col min="1" max="1" width="12.875" customWidth="1"/>
+    <col min="2" max="2" width="17.875" customWidth="1"/>
+    <col min="3" max="3" width="19.875" customWidth="1"/>
+    <col min="4" max="4" width="33.875" customWidth="1"/>
+    <col min="5" max="5" width="14.875" customWidth="1"/>
+    <col min="6" max="6" width="31.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>26</v>
       </c>
@@ -4026,7 +4042,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4046,7 +4062,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4066,7 +4082,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4086,7 +4102,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4107,27 +4123,28 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F5"/>
+  <autoFilter ref="A1:F5" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
+    <ignoredError sqref="A1:F5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="17.83203125" customWidth="1"/>
-    <col min="4" max="4" width="27.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="62.83203125" customWidth="1"/>
+    <col min="1" max="2" width="12.875" customWidth="1"/>
+    <col min="3" max="3" width="17.875" customWidth="1"/>
+    <col min="4" max="4" width="27.875" customWidth="1"/>
+    <col min="5" max="5" width="14.875" customWidth="1"/>
+    <col min="6" max="6" width="12.875" customWidth="1"/>
+    <col min="7" max="7" width="62.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>26</v>
       </c>
@@ -4150,7 +4167,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4173,7 +4190,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4196,7 +4213,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4219,7 +4236,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4242,7 +4259,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4265,7 +4282,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4288,7 +4305,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4311,7 +4328,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4334,7 +4351,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4357,7 +4374,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4380,7 +4397,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4403,7 +4420,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4426,7 +4443,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4449,7 +4466,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4472,7 +4489,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4495,7 +4512,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4518,7 +4535,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4541,7 +4558,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4564,7 +4581,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4587,7 +4604,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4611,27 +4628,29 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G21"/>
+  <autoFilter ref="A1:G21" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G21"/>
+    <ignoredError sqref="A1:G21" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="22.83203125" customWidth="1"/>
-    <col min="3" max="3" width="23.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="46.83203125" customWidth="1"/>
-    <col min="7" max="7" width="62.83203125" customWidth="1"/>
+    <col min="1" max="1" width="12.875" customWidth="1"/>
+    <col min="2" max="2" width="22.875" customWidth="1"/>
+    <col min="3" max="3" width="23.875" customWidth="1"/>
+    <col min="4" max="4" width="14.875" customWidth="1"/>
+    <col min="5" max="5" width="12.875" customWidth="1"/>
+    <col min="6" max="6" width="46.875" customWidth="1"/>
+    <col min="7" max="7" width="62.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>26</v>
       </c>
@@ -4654,7 +4673,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4678,26 +4697,27 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G2" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
+    <ignoredError sqref="A1:G2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F300"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="17.83203125" customWidth="1"/>
-    <col min="4" max="4" width="28.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="1" max="2" width="12.875" customWidth="1"/>
+    <col min="3" max="3" width="17.875" customWidth="1"/>
+    <col min="4" max="4" width="28.875" customWidth="1"/>
+    <col min="5" max="5" width="14.875" customWidth="1"/>
+    <col min="6" max="6" width="12.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>26</v>
       </c>
@@ -4717,7 +4737,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4737,7 +4757,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4757,7 +4777,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4777,7 +4797,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4797,7 +4817,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4817,7 +4837,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4837,7 +4857,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4857,7 +4877,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4877,7 +4897,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4897,7 +4917,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4917,7 +4937,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4937,7 +4957,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4957,7 +4977,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4977,7 +4997,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4997,7 +5017,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -5017,7 +5037,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -5037,7 +5057,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -5057,7 +5077,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -5077,7 +5097,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -5097,7 +5117,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -5117,7 +5137,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -5137,7 +5157,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -5157,7 +5177,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -5177,7 +5197,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -5197,7 +5217,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -5217,7 +5237,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -5237,7 +5257,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -5257,7 +5277,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -5277,7 +5297,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -5297,7 +5317,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -5317,7 +5337,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -5337,7 +5357,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -5357,7 +5377,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -5377,7 +5397,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5397,7 +5417,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5417,7 +5437,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5437,7 +5457,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5457,7 +5477,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5477,7 +5497,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -5497,7 +5517,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -5517,7 +5537,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -5537,7 +5557,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -5557,7 +5577,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -5577,7 +5597,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -5597,7 +5617,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -5617,7 +5637,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -5637,7 +5657,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -5657,7 +5677,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -5677,7 +5697,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -5697,7 +5717,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -5717,7 +5737,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -5737,7 +5757,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -5757,7 +5777,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -5777,7 +5797,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -5797,7 +5817,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -5817,7 +5837,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -5837,7 +5857,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -5857,7 +5877,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -5877,7 +5897,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -5897,7 +5917,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -5917,7 +5937,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -5937,7 +5957,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -5957,7 +5977,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -5977,7 +5997,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -5997,7 +6017,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -6017,7 +6037,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -6037,7 +6057,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -6057,7 +6077,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -6077,7 +6097,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -6097,7 +6117,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -6117,7 +6137,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -6137,7 +6157,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -6157,7 +6177,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -6177,7 +6197,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -6197,7 +6217,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -6217,7 +6237,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
@@ -6237,7 +6257,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -6257,7 +6277,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -6277,7 +6297,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
@@ -6297,7 +6317,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
@@ -6317,7 +6337,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -6337,7 +6357,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -6357,7 +6377,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -6377,7 +6397,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -6397,7 +6417,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -6417,7 +6437,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -6437,7 +6457,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -6457,7 +6477,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -6477,7 +6497,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
@@ -6497,7 +6517,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -6517,7 +6537,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
@@ -6537,7 +6557,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
@@ -6557,7 +6577,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
@@ -6577,7 +6597,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
@@ -6597,7 +6617,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
@@ -6617,7 +6637,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
@@ -6637,7 +6657,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
@@ -6657,7 +6677,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
@@ -6677,7 +6697,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
@@ -6697,7 +6717,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
@@ -6717,7 +6737,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
@@ -6737,7 +6757,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
@@ -6757,7 +6777,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
@@ -6777,7 +6797,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
@@ -6797,7 +6817,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
@@ -6817,7 +6837,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
@@ -6837,7 +6857,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
@@ -6857,7 +6877,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
@@ -6877,7 +6897,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
@@ -6897,7 +6917,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
@@ -6917,7 +6937,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>111</v>
       </c>
@@ -6937,7 +6957,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>112</v>
       </c>
@@ -6957,7 +6977,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
@@ -6977,7 +6997,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>114</v>
       </c>
@@ -6997,7 +7017,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
@@ -7017,7 +7037,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>116</v>
       </c>
@@ -7037,7 +7057,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>117</v>
       </c>
@@ -7057,7 +7077,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>118</v>
       </c>
@@ -7077,7 +7097,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>119</v>
       </c>
@@ -7097,7 +7117,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>120</v>
       </c>
@@ -7117,7 +7137,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>121</v>
       </c>
@@ -7137,7 +7157,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>122</v>
       </c>
@@ -7157,7 +7177,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>123</v>
       </c>
@@ -7177,7 +7197,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>124</v>
       </c>
@@ -7197,7 +7217,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>125</v>
       </c>
@@ -7217,7 +7237,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126</v>
       </c>
@@ -7237,7 +7257,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>127</v>
       </c>
@@ -7257,7 +7277,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>128</v>
       </c>
@@ -7277,7 +7297,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>129</v>
       </c>
@@ -7297,7 +7317,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>130</v>
       </c>
@@ -7317,7 +7337,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>131</v>
       </c>
@@ -7337,7 +7357,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>132</v>
       </c>
@@ -7357,7 +7377,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>133</v>
       </c>
@@ -7377,7 +7397,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>134</v>
       </c>
@@ -7397,7 +7417,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>135</v>
       </c>
@@ -7417,7 +7437,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>136</v>
       </c>
@@ -7437,7 +7457,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>137</v>
       </c>
@@ -7457,7 +7477,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>138</v>
       </c>
@@ -7477,7 +7497,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>139</v>
       </c>
@@ -7497,7 +7517,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>140</v>
       </c>
@@ -7517,7 +7537,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>141</v>
       </c>
@@ -7537,7 +7557,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>142</v>
       </c>
@@ -7557,7 +7577,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>143</v>
       </c>
@@ -7577,7 +7597,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>144</v>
       </c>
@@ -7597,7 +7617,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>145</v>
       </c>
@@ -7617,7 +7637,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>146</v>
       </c>
@@ -7637,7 +7657,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>147</v>
       </c>
@@ -7657,7 +7677,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>148</v>
       </c>
@@ -7677,7 +7697,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>149</v>
       </c>
@@ -7697,7 +7717,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>150</v>
       </c>
@@ -7717,7 +7737,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>151</v>
       </c>
@@ -7737,7 +7757,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>152</v>
       </c>
@@ -7757,7 +7777,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>153</v>
       </c>
@@ -7777,7 +7797,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>154</v>
       </c>
@@ -7797,7 +7817,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>155</v>
       </c>
@@ -7817,7 +7837,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>156</v>
       </c>
@@ -7837,7 +7857,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>157</v>
       </c>
@@ -7857,7 +7877,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>158</v>
       </c>
@@ -7877,7 +7897,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>159</v>
       </c>
@@ -7897,7 +7917,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>160</v>
       </c>
@@ -7917,7 +7937,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>161</v>
       </c>
@@ -7937,7 +7957,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>162</v>
       </c>
@@ -7957,7 +7977,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>163</v>
       </c>
@@ -7977,7 +7997,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>164</v>
       </c>
@@ -7997,7 +8017,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>165</v>
       </c>
@@ -8017,7 +8037,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>166</v>
       </c>
@@ -8037,7 +8057,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>167</v>
       </c>
@@ -8057,7 +8077,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>168</v>
       </c>
@@ -8077,7 +8097,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>169</v>
       </c>
@@ -8097,7 +8117,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>170</v>
       </c>
@@ -8117,7 +8137,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>171</v>
       </c>
@@ -8137,7 +8157,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>172</v>
       </c>
@@ -8157,7 +8177,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>173</v>
       </c>
@@ -8177,7 +8197,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>174</v>
       </c>
@@ -8197,7 +8217,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>175</v>
       </c>
@@ -8217,7 +8237,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>176</v>
       </c>
@@ -8237,7 +8257,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>177</v>
       </c>
@@ -8257,7 +8277,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>178</v>
       </c>
@@ -8277,7 +8297,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>179</v>
       </c>
@@ -8297,7 +8317,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>180</v>
       </c>
@@ -8317,7 +8337,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>181</v>
       </c>
@@ -8337,7 +8357,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>182</v>
       </c>
@@ -8357,7 +8377,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>183</v>
       </c>
@@ -8377,7 +8397,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>184</v>
       </c>
@@ -8397,7 +8417,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>185</v>
       </c>
@@ -8417,7 +8437,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>186</v>
       </c>
@@ -8437,7 +8457,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>187</v>
       </c>
@@ -8457,7 +8477,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>188</v>
       </c>
@@ -8477,7 +8497,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>189</v>
       </c>
@@ -8497,7 +8517,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>190</v>
       </c>
@@ -8517,7 +8537,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>191</v>
       </c>
@@ -8537,7 +8557,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>192</v>
       </c>
@@ -8557,7 +8577,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>193</v>
       </c>
@@ -8577,7 +8597,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>194</v>
       </c>
@@ -8597,7 +8617,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>195</v>
       </c>
@@ -8617,7 +8637,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>196</v>
       </c>
@@ -8637,7 +8657,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="198">
+    <row r="198" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>197</v>
       </c>
@@ -8657,7 +8677,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="199">
+    <row r="199" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>198</v>
       </c>
@@ -8677,7 +8697,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="200">
+    <row r="200" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>199</v>
       </c>
@@ -8697,7 +8717,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="201">
+    <row r="201" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>200</v>
       </c>
@@ -8717,7 +8737,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="202">
+    <row r="202" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>201</v>
       </c>
@@ -8737,7 +8757,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>202</v>
       </c>
@@ -8757,7 +8777,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>203</v>
       </c>
@@ -8777,7 +8797,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="205">
+    <row r="205" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>204</v>
       </c>
@@ -8797,7 +8817,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="206">
+    <row r="206" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>205</v>
       </c>
@@ -8817,7 +8837,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="207">
+    <row r="207" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>206</v>
       </c>
@@ -8837,7 +8857,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="208">
+    <row r="208" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>207</v>
       </c>
@@ -8857,7 +8877,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="209">
+    <row r="209" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>208</v>
       </c>
@@ -8877,7 +8897,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="210">
+    <row r="210" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>209</v>
       </c>
@@ -8897,7 +8917,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="211">
+    <row r="211" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>210</v>
       </c>
@@ -8917,7 +8937,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="212">
+    <row r="212" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>211</v>
       </c>
@@ -8937,7 +8957,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="213">
+    <row r="213" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>212</v>
       </c>
@@ -8957,7 +8977,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="214">
+    <row r="214" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>213</v>
       </c>
@@ -8977,7 +8997,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="215">
+    <row r="215" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>214</v>
       </c>
@@ -8997,7 +9017,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="216">
+    <row r="216" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>215</v>
       </c>
@@ -9017,7 +9037,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="217">
+    <row r="217" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>216</v>
       </c>
@@ -9037,7 +9057,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="218">
+    <row r="218" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>217</v>
       </c>
@@ -9057,7 +9077,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="219">
+    <row r="219" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>218</v>
       </c>
@@ -9077,7 +9097,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="220">
+    <row r="220" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>219</v>
       </c>
@@ -9097,7 +9117,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="221">
+    <row r="221" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>220</v>
       </c>
@@ -9117,7 +9137,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="222">
+    <row r="222" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>221</v>
       </c>
@@ -9137,7 +9157,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="223">
+    <row r="223" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>222</v>
       </c>
@@ -9157,7 +9177,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="224">
+    <row r="224" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>223</v>
       </c>
@@ -9177,7 +9197,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="225">
+    <row r="225" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>224</v>
       </c>
@@ -9197,7 +9217,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="226">
+    <row r="226" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>225</v>
       </c>
@@ -9217,7 +9237,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="227">
+    <row r="227" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>226</v>
       </c>
@@ -9237,7 +9257,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="228">
+    <row r="228" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>227</v>
       </c>
@@ -9257,7 +9277,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="229">
+    <row r="229" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>228</v>
       </c>
@@ -9277,7 +9297,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="230">
+    <row r="230" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>229</v>
       </c>
@@ -9297,7 +9317,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="231">
+    <row r="231" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>230</v>
       </c>
@@ -9317,7 +9337,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="232">
+    <row r="232" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>231</v>
       </c>
@@ -9337,7 +9357,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="233">
+    <row r="233" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>232</v>
       </c>
@@ -9357,7 +9377,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="234">
+    <row r="234" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>233</v>
       </c>
@@ -9377,7 +9397,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="235">
+    <row r="235" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>234</v>
       </c>
@@ -9397,7 +9417,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="236">
+    <row r="236" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>235</v>
       </c>
@@ -9417,7 +9437,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="237">
+    <row r="237" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>236</v>
       </c>
@@ -9437,7 +9457,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="238">
+    <row r="238" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>237</v>
       </c>
@@ -9457,7 +9477,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="239">
+    <row r="239" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>238</v>
       </c>
@@ -9477,7 +9497,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="240">
+    <row r="240" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>239</v>
       </c>
@@ -9497,7 +9517,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="241">
+    <row r="241" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>240</v>
       </c>
@@ -9517,7 +9537,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="242">
+    <row r="242" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>241</v>
       </c>
@@ -9537,7 +9557,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="243">
+    <row r="243" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>242</v>
       </c>
@@ -9557,7 +9577,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="244">
+    <row r="244" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>243</v>
       </c>
@@ -9577,7 +9597,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="245">
+    <row r="245" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>244</v>
       </c>
@@ -9597,7 +9617,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="246">
+    <row r="246" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>245</v>
       </c>
@@ -9617,7 +9637,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="247">
+    <row r="247" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>246</v>
       </c>
@@ -9637,7 +9657,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="248">
+    <row r="248" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>247</v>
       </c>
@@ -9657,7 +9677,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="249">
+    <row r="249" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>248</v>
       </c>
@@ -9677,7 +9697,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="250">
+    <row r="250" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>249</v>
       </c>
@@ -9697,7 +9717,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="251">
+    <row r="251" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>250</v>
       </c>
@@ -9717,7 +9737,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="252">
+    <row r="252" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>251</v>
       </c>
@@ -9737,7 +9757,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="253">
+    <row r="253" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>252</v>
       </c>
@@ -9757,7 +9777,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="254">
+    <row r="254" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>253</v>
       </c>
@@ -9777,7 +9797,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="255">
+    <row r="255" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>254</v>
       </c>
@@ -9797,7 +9817,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="256">
+    <row r="256" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>255</v>
       </c>
@@ -9817,7 +9837,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="257">
+    <row r="257" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>256</v>
       </c>
@@ -9837,7 +9857,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="258">
+    <row r="258" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>257</v>
       </c>
@@ -9857,7 +9877,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="259">
+    <row r="259" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>258</v>
       </c>
@@ -9877,7 +9897,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="260">
+    <row r="260" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>259</v>
       </c>
@@ -9897,7 +9917,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="261">
+    <row r="261" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>260</v>
       </c>
@@ -9917,7 +9937,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="262">
+    <row r="262" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>261</v>
       </c>
@@ -9937,7 +9957,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="263">
+    <row r="263" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>262</v>
       </c>
@@ -9957,7 +9977,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="264">
+    <row r="264" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>263</v>
       </c>
@@ -9977,7 +9997,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="265">
+    <row r="265" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>264</v>
       </c>
@@ -9997,7 +10017,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="266">
+    <row r="266" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>265</v>
       </c>
@@ -10017,7 +10037,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="267">
+    <row r="267" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>266</v>
       </c>
@@ -10037,7 +10057,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="268">
+    <row r="268" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>267</v>
       </c>
@@ -10057,7 +10077,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="269">
+    <row r="269" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>268</v>
       </c>
@@ -10077,7 +10097,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="270">
+    <row r="270" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>269</v>
       </c>
@@ -10097,7 +10117,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="271">
+    <row r="271" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>270</v>
       </c>
@@ -10117,7 +10137,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="272">
+    <row r="272" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>271</v>
       </c>
@@ -10137,7 +10157,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="273">
+    <row r="273" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>272</v>
       </c>
@@ -10157,7 +10177,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="274">
+    <row r="274" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>273</v>
       </c>
@@ -10177,7 +10197,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="275">
+    <row r="275" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>274</v>
       </c>
@@ -10197,7 +10217,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="276">
+    <row r="276" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>275</v>
       </c>
@@ -10217,7 +10237,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="277">
+    <row r="277" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>276</v>
       </c>
@@ -10237,7 +10257,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="278">
+    <row r="278" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>277</v>
       </c>
@@ -10257,7 +10277,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="279">
+    <row r="279" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>278</v>
       </c>
@@ -10277,7 +10297,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="280">
+    <row r="280" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>279</v>
       </c>
@@ -10297,7 +10317,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="281">
+    <row r="281" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>280</v>
       </c>
@@ -10317,7 +10337,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="282">
+    <row r="282" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>281</v>
       </c>
@@ -10337,7 +10357,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="283">
+    <row r="283" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>282</v>
       </c>
@@ -10357,7 +10377,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="284">
+    <row r="284" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>283</v>
       </c>
@@ -10377,7 +10397,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="285">
+    <row r="285" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>284</v>
       </c>
@@ -10397,7 +10417,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="286">
+    <row r="286" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>285</v>
       </c>
@@ -10417,7 +10437,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="287">
+    <row r="287" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>286</v>
       </c>
@@ -10437,7 +10457,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="288">
+    <row r="288" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>287</v>
       </c>
@@ -10457,7 +10477,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="289">
+    <row r="289" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>288</v>
       </c>
@@ -10477,7 +10497,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="290">
+    <row r="290" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>289</v>
       </c>
@@ -10497,7 +10517,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="291">
+    <row r="291" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>290</v>
       </c>
@@ -10517,7 +10537,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="292">
+    <row r="292" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>291</v>
       </c>
@@ -10537,7 +10557,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="293">
+    <row r="293" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>292</v>
       </c>
@@ -10557,7 +10577,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="294">
+    <row r="294" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>293</v>
       </c>
@@ -10577,7 +10597,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="295">
+    <row r="295" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>294</v>
       </c>
@@ -10597,7 +10617,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="296">
+    <row r="296" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>295</v>
       </c>
@@ -10617,7 +10637,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="297">
+    <row r="297" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>296</v>
       </c>
@@ -10637,7 +10657,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="298">
+    <row r="298" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>297</v>
       </c>
@@ -10657,7 +10677,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="299">
+    <row r="299" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>298</v>
       </c>
@@ -10677,7 +10697,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="300">
+    <row r="300" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>299</v>
       </c>
@@ -10698,32 +10718,33 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F300"/>
+  <autoFilter ref="A1:F300" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F300"/>
+    <ignoredError sqref="A1:F300" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:L31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="23.83203125" customWidth="1"/>
-    <col min="3" max="3" width="32.83203125" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" customWidth="1"/>
-    <col min="8" max="8" width="27.83203125" customWidth="1"/>
-    <col min="9" max="9" width="17.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
-    <col min="11" max="11" width="62.83203125" customWidth="1"/>
-    <col min="12" max="12" width="62.83203125" customWidth="1"/>
+    <col min="1" max="1" width="12.875" customWidth="1"/>
+    <col min="2" max="2" width="23.875" customWidth="1"/>
+    <col min="3" max="3" width="32.875" customWidth="1"/>
+    <col min="4" max="4" width="15.875" customWidth="1"/>
+    <col min="5" max="5" width="12.875" customWidth="1"/>
+    <col min="6" max="6" width="20.875" customWidth="1"/>
+    <col min="7" max="7" width="12.875" customWidth="1"/>
+    <col min="8" max="8" width="27.875" customWidth="1"/>
+    <col min="9" max="9" width="17.875" customWidth="1"/>
+    <col min="10" max="10" width="12.875" customWidth="1"/>
+    <col min="11" max="12" width="62.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>26</v>
       </c>
@@ -10761,7 +10782,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -10799,7 +10820,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -10837,7 +10858,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -10875,7 +10896,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -10913,7 +10934,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -10951,7 +10972,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -10989,7 +11010,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -11027,7 +11048,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -11065,7 +11086,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -11103,7 +11124,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -11141,7 +11162,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -11179,7 +11200,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -11217,7 +11238,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -11255,7 +11276,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -11293,7 +11314,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -11331,7 +11352,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -11369,7 +11390,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -11407,7 +11428,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -11445,7 +11466,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -11483,7 +11504,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -11521,7 +11542,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -11559,7 +11580,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -11597,7 +11618,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -11635,7 +11656,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -11673,7 +11694,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -11711,7 +11732,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -11749,7 +11770,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -11787,7 +11808,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -11825,7 +11846,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -11863,7 +11884,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -11902,26 +11923,28 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L31"/>
+  <autoFilter ref="A1:L31" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError sqref="A1:L31" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F326"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.83203125" customWidth="1"/>
-    <col min="2" max="2" width="17.83203125" customWidth="1"/>
-    <col min="3" max="3" width="26.83203125" customWidth="1"/>
-    <col min="4" max="4" width="35.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="62.83203125" customWidth="1"/>
+    <col min="1" max="1" width="19.875" customWidth="1"/>
+    <col min="2" max="2" width="17.875" customWidth="1"/>
+    <col min="3" max="3" width="26.875" customWidth="1"/>
+    <col min="4" max="4" width="35.875" customWidth="1"/>
+    <col min="5" max="5" width="14.875" customWidth="1"/>
+    <col min="6" max="6" width="62.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1143</v>
       </c>
@@ -11941,7 +11964,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1144</v>
       </c>
@@ -11961,7 +11984,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1144</v>
       </c>
@@ -11981,7 +12004,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1144</v>
       </c>
@@ -12001,7 +12024,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1144</v>
       </c>
@@ -12021,7 +12044,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1145</v>
       </c>
@@ -12041,7 +12064,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1145</v>
       </c>
@@ -12061,7 +12084,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1145</v>
       </c>
@@ -12081,7 +12104,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1145</v>
       </c>
@@ -12101,7 +12124,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1145</v>
       </c>
@@ -12121,7 +12144,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1145</v>
       </c>
@@ -12141,7 +12164,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1145</v>
       </c>
@@ -12161,7 +12184,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>1145</v>
       </c>
@@ -12181,7 +12204,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1145</v>
       </c>
@@ -12201,7 +12224,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>1145</v>
       </c>
@@ -12221,7 +12244,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>1145</v>
       </c>
@@ -12241,7 +12264,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>1145</v>
       </c>
@@ -12261,7 +12284,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>1145</v>
       </c>
@@ -12281,7 +12304,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>1145</v>
       </c>
@@ -12301,7 +12324,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>1145</v>
       </c>
@@ -12321,7 +12344,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>1145</v>
       </c>
@@ -12341,7 +12364,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>1145</v>
       </c>
@@ -12361,7 +12384,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>1145</v>
       </c>
@@ -12381,7 +12404,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>1145</v>
       </c>
@@ -12401,7 +12424,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>1145</v>
       </c>
@@ -12421,7 +12444,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>1146</v>
       </c>
@@ -12441,7 +12464,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>1148</v>
       </c>
@@ -12461,7 +12484,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>1148</v>
       </c>
@@ -12481,7 +12504,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>1148</v>
       </c>
@@ -12501,7 +12524,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>1148</v>
       </c>
@@ -12521,7 +12544,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>1148</v>
       </c>
@@ -12541,7 +12564,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>1148</v>
       </c>
@@ -12561,7 +12584,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>1148</v>
       </c>
@@ -12581,7 +12604,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>1148</v>
       </c>
@@ -12601,7 +12624,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>1148</v>
       </c>
@@ -12621,7 +12644,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>1148</v>
       </c>
@@ -12641,7 +12664,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>1148</v>
       </c>
@@ -12661,7 +12684,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>1148</v>
       </c>
@@ -12681,7 +12704,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>1148</v>
       </c>
@@ -12701,7 +12724,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>1148</v>
       </c>
@@ -12721,7 +12744,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>1148</v>
       </c>
@@ -12741,7 +12764,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>1148</v>
       </c>
@@ -12761,7 +12784,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>1148</v>
       </c>
@@ -12781,7 +12804,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>1148</v>
       </c>
@@ -12801,7 +12824,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>1148</v>
       </c>
@@ -12821,7 +12844,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>1148</v>
       </c>
@@ -12841,7 +12864,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>1148</v>
       </c>
@@ -12861,7 +12884,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>1148</v>
       </c>
@@ -12881,7 +12904,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>1148</v>
       </c>
@@ -12901,7 +12924,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>1148</v>
       </c>
@@ -12921,7 +12944,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>1148</v>
       </c>
@@ -12941,7 +12964,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>1148</v>
       </c>
@@ -12961,7 +12984,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>1148</v>
       </c>
@@ -12981,7 +13004,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>1148</v>
       </c>
@@ -13001,7 +13024,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>1148</v>
       </c>
@@ -13021,7 +13044,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>1148</v>
       </c>
@@ -13041,7 +13064,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>1148</v>
       </c>
@@ -13061,7 +13084,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>1148</v>
       </c>
@@ -13081,7 +13104,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>1148</v>
       </c>
@@ -13101,7 +13124,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>1148</v>
       </c>
@@ -13121,7 +13144,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>1148</v>
       </c>
@@ -13141,7 +13164,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>1148</v>
       </c>
@@ -13161,7 +13184,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>1148</v>
       </c>
@@ -13181,7 +13204,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>1148</v>
       </c>
@@ -13201,7 +13224,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>1148</v>
       </c>
@@ -13221,7 +13244,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>1148</v>
       </c>
@@ -13241,7 +13264,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>1148</v>
       </c>
@@ -13261,7 +13284,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>1148</v>
       </c>
@@ -13281,7 +13304,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>1148</v>
       </c>
@@ -13301,7 +13324,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>1148</v>
       </c>
@@ -13321,7 +13344,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>1148</v>
       </c>
@@ -13341,7 +13364,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>1148</v>
       </c>
@@ -13361,7 +13384,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>1148</v>
       </c>
@@ -13381,7 +13404,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>1148</v>
       </c>
@@ -13401,7 +13424,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>1148</v>
       </c>
@@ -13421,7 +13444,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>1148</v>
       </c>
@@ -13441,7 +13464,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>1148</v>
       </c>
@@ -13461,7 +13484,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>1148</v>
       </c>
@@ -13481,7 +13504,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>1148</v>
       </c>
@@ -13501,7 +13524,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>1148</v>
       </c>
@@ -13521,7 +13544,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>1148</v>
       </c>
@@ -13541,7 +13564,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>1148</v>
       </c>
@@ -13561,7 +13584,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>1148</v>
       </c>
@@ -13581,7 +13604,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>1148</v>
       </c>
@@ -13601,7 +13624,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>1148</v>
       </c>
@@ -13621,7 +13644,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>1148</v>
       </c>
@@ -13641,7 +13664,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>1148</v>
       </c>
@@ -13661,7 +13684,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>1148</v>
       </c>
@@ -13681,7 +13704,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>1148</v>
       </c>
@@ -13701,7 +13724,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>1148</v>
       </c>
@@ -13721,7 +13744,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>1148</v>
       </c>
@@ -13741,7 +13764,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>1148</v>
       </c>
@@ -13761,7 +13784,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>1148</v>
       </c>
@@ -13781,7 +13804,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>1148</v>
       </c>
@@ -13801,7 +13824,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>1148</v>
       </c>
@@ -13821,7 +13844,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>1148</v>
       </c>
@@ -13841,7 +13864,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>1148</v>
       </c>
@@ -13861,7 +13884,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>1148</v>
       </c>
@@ -13881,7 +13904,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>1148</v>
       </c>
@@ -13901,7 +13924,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>1148</v>
       </c>
@@ -13921,7 +13944,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>1148</v>
       </c>
@@ -13941,7 +13964,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>1148</v>
       </c>
@@ -13961,7 +13984,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>1148</v>
       </c>
@@ -13981,7 +14004,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>1148</v>
       </c>
@@ -14001,7 +14024,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>1148</v>
       </c>
@@ -14021,7 +14044,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>1148</v>
       </c>
@@ -14041,7 +14064,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>1148</v>
       </c>
@@ -14061,7 +14084,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>1148</v>
       </c>
@@ -14081,7 +14104,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>1148</v>
       </c>
@@ -14101,7 +14124,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>1148</v>
       </c>
@@ -14121,7 +14144,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>1148</v>
       </c>
@@ -14141,7 +14164,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>1148</v>
       </c>
@@ -14161,7 +14184,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>1148</v>
       </c>
@@ -14181,7 +14204,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>1148</v>
       </c>
@@ -14201,7 +14224,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>1148</v>
       </c>
@@ -14221,7 +14244,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>1148</v>
       </c>
@@ -14241,7 +14264,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>1148</v>
       </c>
@@ -14261,7 +14284,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>1148</v>
       </c>
@@ -14281,7 +14304,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>1148</v>
       </c>
@@ -14301,7 +14324,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>1148</v>
       </c>
@@ -14321,7 +14344,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>1148</v>
       </c>
@@ -14341,7 +14364,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>1148</v>
       </c>
@@ -14361,7 +14384,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>1148</v>
       </c>
@@ -14381,7 +14404,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>1148</v>
       </c>
@@ -14401,7 +14424,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>1148</v>
       </c>
@@ -14421,7 +14444,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>1148</v>
       </c>
@@ -14441,7 +14464,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>1148</v>
       </c>
@@ -14461,7 +14484,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>1148</v>
       </c>
@@ -14481,7 +14504,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>1148</v>
       </c>
@@ -14501,7 +14524,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>1148</v>
       </c>
@@ -14521,7 +14544,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>1148</v>
       </c>
@@ -14541,7 +14564,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>1148</v>
       </c>
@@ -14561,7 +14584,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>1148</v>
       </c>
@@ -14581,7 +14604,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>1148</v>
       </c>
@@ -14601,7 +14624,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>1148</v>
       </c>
@@ -14621,7 +14644,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>1148</v>
       </c>
@@ -14641,7 +14664,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>1148</v>
       </c>
@@ -14661,7 +14684,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>1148</v>
       </c>
@@ -14681,7 +14704,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>1148</v>
       </c>
@@ -14701,7 +14724,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>1148</v>
       </c>
@@ -14721,7 +14744,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>1148</v>
       </c>
@@ -14741,7 +14764,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>1148</v>
       </c>
@@ -14761,7 +14784,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>1148</v>
       </c>
@@ -14781,7 +14804,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>1148</v>
       </c>
@@ -14801,7 +14824,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>1148</v>
       </c>
@@ -14821,7 +14844,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>1148</v>
       </c>
@@ -14841,7 +14864,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>1148</v>
       </c>
@@ -14861,7 +14884,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>1148</v>
       </c>
@@ -14881,7 +14904,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>1148</v>
       </c>
@@ -14901,7 +14924,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>1148</v>
       </c>
@@ -14921,7 +14944,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>1148</v>
       </c>
@@ -14941,7 +14964,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>1148</v>
       </c>
@@ -14961,7 +14984,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>1148</v>
       </c>
@@ -14981,7 +15004,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>1148</v>
       </c>
@@ -15001,7 +15024,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>1148</v>
       </c>
@@ -15021,7 +15044,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>1148</v>
       </c>
@@ -15041,7 +15064,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>1148</v>
       </c>
@@ -15061,7 +15084,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>1148</v>
       </c>
@@ -15081,7 +15104,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>1148</v>
       </c>
@@ -15101,7 +15124,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>1148</v>
       </c>
@@ -15121,7 +15144,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>1148</v>
       </c>
@@ -15141,7 +15164,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>1148</v>
       </c>
@@ -15161,7 +15184,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>1148</v>
       </c>
@@ -15181,7 +15204,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>1148</v>
       </c>
@@ -15201,7 +15224,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>1148</v>
       </c>
@@ -15221,7 +15244,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>1148</v>
       </c>
@@ -15241,7 +15264,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>1148</v>
       </c>
@@ -15261,7 +15284,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>1148</v>
       </c>
@@ -15281,7 +15304,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>1148</v>
       </c>
@@ -15301,7 +15324,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>1148</v>
       </c>
@@ -15321,7 +15344,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>1148</v>
       </c>
@@ -15341,7 +15364,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>1148</v>
       </c>
@@ -15361,7 +15384,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>1148</v>
       </c>
@@ -15381,7 +15404,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>1148</v>
       </c>
@@ -15401,7 +15424,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>1148</v>
       </c>
@@ -15421,7 +15444,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>1148</v>
       </c>
@@ -15441,7 +15464,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>1148</v>
       </c>
@@ -15461,7 +15484,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>1148</v>
       </c>
@@ -15481,7 +15504,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>1148</v>
       </c>
@@ -15501,7 +15524,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>1148</v>
       </c>
@@ -15521,7 +15544,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>1148</v>
       </c>
@@ -15541,7 +15564,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>1148</v>
       </c>
@@ -15561,7 +15584,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>1148</v>
       </c>
@@ -15581,7 +15604,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>1148</v>
       </c>
@@ -15601,7 +15624,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>1148</v>
       </c>
@@ -15621,7 +15644,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>1148</v>
       </c>
@@ -15641,7 +15664,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>1148</v>
       </c>
@@ -15661,7 +15684,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>1148</v>
       </c>
@@ -15681,7 +15704,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>1148</v>
       </c>
@@ -15701,7 +15724,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>1148</v>
       </c>
@@ -15721,7 +15744,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>1148</v>
       </c>
@@ -15741,7 +15764,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>1148</v>
       </c>
@@ -15761,7 +15784,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>1148</v>
       </c>
@@ -15781,7 +15804,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>1148</v>
       </c>
@@ -15801,7 +15824,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>1148</v>
       </c>
@@ -15821,7 +15844,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>1148</v>
       </c>
@@ -15841,7 +15864,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>1148</v>
       </c>
@@ -15861,7 +15884,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="198">
+    <row r="198" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>1148</v>
       </c>
@@ -15881,7 +15904,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="199">
+    <row r="199" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>1148</v>
       </c>
@@ -15901,7 +15924,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="200">
+    <row r="200" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>1148</v>
       </c>
@@ -15921,7 +15944,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="201">
+    <row r="201" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>1148</v>
       </c>
@@ -15941,7 +15964,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="202">
+    <row r="202" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>1148</v>
       </c>
@@ -15961,7 +15984,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>1148</v>
       </c>
@@ -15981,7 +16004,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>1148</v>
       </c>
@@ -16001,7 +16024,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="205">
+    <row r="205" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>1148</v>
       </c>
@@ -16021,7 +16044,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="206">
+    <row r="206" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>1148</v>
       </c>
@@ -16041,7 +16064,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="207">
+    <row r="207" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>1148</v>
       </c>
@@ -16061,7 +16084,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="208">
+    <row r="208" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>1148</v>
       </c>
@@ -16081,7 +16104,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="209">
+    <row r="209" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>1148</v>
       </c>
@@ -16101,7 +16124,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="210">
+    <row r="210" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>1148</v>
       </c>
@@ -16121,7 +16144,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="211">
+    <row r="211" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>1148</v>
       </c>
@@ -16141,7 +16164,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="212">
+    <row r="212" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>1148</v>
       </c>
@@ -16161,7 +16184,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="213">
+    <row r="213" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>1148</v>
       </c>
@@ -16181,7 +16204,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="214">
+    <row r="214" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>1148</v>
       </c>
@@ -16201,7 +16224,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="215">
+    <row r="215" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>1148</v>
       </c>
@@ -16221,7 +16244,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="216">
+    <row r="216" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>1148</v>
       </c>
@@ -16241,7 +16264,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="217">
+    <row r="217" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>1148</v>
       </c>
@@ -16261,7 +16284,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="218">
+    <row r="218" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>1148</v>
       </c>
@@ -16281,7 +16304,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="219">
+    <row r="219" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>1148</v>
       </c>
@@ -16301,7 +16324,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="220">
+    <row r="220" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>1148</v>
       </c>
@@ -16321,7 +16344,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="221">
+    <row r="221" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>1148</v>
       </c>
@@ -16341,7 +16364,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="222">
+    <row r="222" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>1148</v>
       </c>
@@ -16361,7 +16384,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="223">
+    <row r="223" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>1148</v>
       </c>
@@ -16381,7 +16404,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="224">
+    <row r="224" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>1148</v>
       </c>
@@ -16401,7 +16424,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="225">
+    <row r="225" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>1148</v>
       </c>
@@ -16421,7 +16444,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="226">
+    <row r="226" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>1148</v>
       </c>
@@ -16441,7 +16464,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="227">
+    <row r="227" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>1148</v>
       </c>
@@ -16461,7 +16484,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="228">
+    <row r="228" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>1148</v>
       </c>
@@ -16481,7 +16504,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="229">
+    <row r="229" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>1148</v>
       </c>
@@ -16501,7 +16524,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="230">
+    <row r="230" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>1148</v>
       </c>
@@ -16521,7 +16544,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="231">
+    <row r="231" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>1148</v>
       </c>
@@ -16541,7 +16564,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="232">
+    <row r="232" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>1148</v>
       </c>
@@ -16561,7 +16584,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="233">
+    <row r="233" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>1148</v>
       </c>
@@ -16581,7 +16604,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="234">
+    <row r="234" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>1148</v>
       </c>
@@ -16601,7 +16624,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="235">
+    <row r="235" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>1148</v>
       </c>
@@ -16621,7 +16644,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="236">
+    <row r="236" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>1148</v>
       </c>
@@ -16641,7 +16664,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="237">
+    <row r="237" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>1148</v>
       </c>
@@ -16661,7 +16684,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="238">
+    <row r="238" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>1148</v>
       </c>
@@ -16681,7 +16704,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="239">
+    <row r="239" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>1148</v>
       </c>
@@ -16701,7 +16724,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="240">
+    <row r="240" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>1148</v>
       </c>
@@ -16721,7 +16744,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="241">
+    <row r="241" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>1148</v>
       </c>
@@ -16741,7 +16764,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="242">
+    <row r="242" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>1148</v>
       </c>
@@ -16761,7 +16784,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="243">
+    <row r="243" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>1148</v>
       </c>
@@ -16781,7 +16804,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="244">
+    <row r="244" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>1148</v>
       </c>
@@ -16801,7 +16824,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="245">
+    <row r="245" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>1148</v>
       </c>
@@ -16821,7 +16844,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="246">
+    <row r="246" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>1148</v>
       </c>
@@ -16841,7 +16864,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="247">
+    <row r="247" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>1148</v>
       </c>
@@ -16861,7 +16884,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="248">
+    <row r="248" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>1148</v>
       </c>
@@ -16881,7 +16904,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="249">
+    <row r="249" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>1148</v>
       </c>
@@ -16901,7 +16924,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="250">
+    <row r="250" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>1148</v>
       </c>
@@ -16921,7 +16944,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="251">
+    <row r="251" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>1148</v>
       </c>
@@ -16941,7 +16964,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="252">
+    <row r="252" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>1148</v>
       </c>
@@ -16961,7 +16984,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="253">
+    <row r="253" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>1148</v>
       </c>
@@ -16981,7 +17004,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="254">
+    <row r="254" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>1148</v>
       </c>
@@ -17001,7 +17024,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="255">
+    <row r="255" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>1148</v>
       </c>
@@ -17021,7 +17044,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="256">
+    <row r="256" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>1148</v>
       </c>
@@ -17041,7 +17064,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="257">
+    <row r="257" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>1148</v>
       </c>
@@ -17061,7 +17084,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="258">
+    <row r="258" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>1148</v>
       </c>
@@ -17081,7 +17104,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="259">
+    <row r="259" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>1148</v>
       </c>
@@ -17101,7 +17124,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="260">
+    <row r="260" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>1148</v>
       </c>
@@ -17121,7 +17144,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="261">
+    <row r="261" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>1148</v>
       </c>
@@ -17141,7 +17164,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="262">
+    <row r="262" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>1148</v>
       </c>
@@ -17161,7 +17184,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="263">
+    <row r="263" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>1148</v>
       </c>
@@ -17181,7 +17204,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="264">
+    <row r="264" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>1148</v>
       </c>
@@ -17201,7 +17224,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="265">
+    <row r="265" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>1148</v>
       </c>
@@ -17221,7 +17244,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="266">
+    <row r="266" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>1148</v>
       </c>
@@ -17241,7 +17264,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="267">
+    <row r="267" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>1148</v>
       </c>
@@ -17261,7 +17284,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="268">
+    <row r="268" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>1148</v>
       </c>
@@ -17281,7 +17304,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="269">
+    <row r="269" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>1148</v>
       </c>
@@ -17301,7 +17324,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="270">
+    <row r="270" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>1148</v>
       </c>
@@ -17321,7 +17344,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="271">
+    <row r="271" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>1148</v>
       </c>
@@ -17341,7 +17364,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="272">
+    <row r="272" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>1148</v>
       </c>
@@ -17361,7 +17384,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="273">
+    <row r="273" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>1148</v>
       </c>
@@ -17381,7 +17404,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="274">
+    <row r="274" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>1148</v>
       </c>
@@ -17401,7 +17424,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="275">
+    <row r="275" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>1148</v>
       </c>
@@ -17421,7 +17444,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="276">
+    <row r="276" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>1148</v>
       </c>
@@ -17441,7 +17464,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="277">
+    <row r="277" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>1148</v>
       </c>
@@ -17461,7 +17484,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="278">
+    <row r="278" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>1148</v>
       </c>
@@ -17481,7 +17504,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="279">
+    <row r="279" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>1148</v>
       </c>
@@ -17501,7 +17524,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="280">
+    <row r="280" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>1148</v>
       </c>
@@ -17521,7 +17544,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="281">
+    <row r="281" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>1148</v>
       </c>
@@ -17541,7 +17564,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="282">
+    <row r="282" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>1148</v>
       </c>
@@ -17561,7 +17584,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="283">
+    <row r="283" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>1148</v>
       </c>
@@ -17581,7 +17604,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="284">
+    <row r="284" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>1148</v>
       </c>
@@ -17601,7 +17624,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="285">
+    <row r="285" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>1148</v>
       </c>
@@ -17621,7 +17644,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="286">
+    <row r="286" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>1148</v>
       </c>
@@ -17641,7 +17664,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="287">
+    <row r="287" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>1148</v>
       </c>
@@ -17661,7 +17684,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="288">
+    <row r="288" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>1148</v>
       </c>
@@ -17681,7 +17704,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="289">
+    <row r="289" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>1148</v>
       </c>
@@ -17701,7 +17724,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="290">
+    <row r="290" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>1148</v>
       </c>
@@ -17721,7 +17744,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="291">
+    <row r="291" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>1148</v>
       </c>
@@ -17741,7 +17764,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="292">
+    <row r="292" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>1148</v>
       </c>
@@ -17761,7 +17784,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="293">
+    <row r="293" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>1148</v>
       </c>
@@ -17781,7 +17804,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="294">
+    <row r="294" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>1148</v>
       </c>
@@ -17801,7 +17824,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="295">
+    <row r="295" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>1148</v>
       </c>
@@ -17821,7 +17844,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="296">
+    <row r="296" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>1148</v>
       </c>
@@ -17841,7 +17864,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="297">
+    <row r="297" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>1148</v>
       </c>
@@ -17861,7 +17884,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="298">
+    <row r="298" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>1148</v>
       </c>
@@ -17881,7 +17904,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="299">
+    <row r="299" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>1148</v>
       </c>
@@ -17901,7 +17924,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="300">
+    <row r="300" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>1148</v>
       </c>
@@ -17921,7 +17944,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="301">
+    <row r="301" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>1148</v>
       </c>
@@ -17941,7 +17964,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="302">
+    <row r="302" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>1148</v>
       </c>
@@ -17961,7 +17984,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="303">
+    <row r="303" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>1148</v>
       </c>
@@ -17981,7 +18004,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="304">
+    <row r="304" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>1148</v>
       </c>
@@ -18001,7 +18024,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="305">
+    <row r="305" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>1148</v>
       </c>
@@ -18021,7 +18044,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="306">
+    <row r="306" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>1148</v>
       </c>
@@ -18041,7 +18064,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="307">
+    <row r="307" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>1148</v>
       </c>
@@ -18061,7 +18084,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="308">
+    <row r="308" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>1148</v>
       </c>
@@ -18081,7 +18104,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="309">
+    <row r="309" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>1148</v>
       </c>
@@ -18101,7 +18124,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="310">
+    <row r="310" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>1148</v>
       </c>
@@ -18121,7 +18144,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="311">
+    <row r="311" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>1148</v>
       </c>
@@ -18141,7 +18164,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="312">
+    <row r="312" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>1148</v>
       </c>
@@ -18161,7 +18184,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="313">
+    <row r="313" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>1148</v>
       </c>
@@ -18181,7 +18204,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="314">
+    <row r="314" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>1148</v>
       </c>
@@ -18201,7 +18224,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="315">
+    <row r="315" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>1148</v>
       </c>
@@ -18221,7 +18244,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="316">
+    <row r="316" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>1148</v>
       </c>
@@ -18241,7 +18264,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="317">
+    <row r="317" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>1148</v>
       </c>
@@ -18261,7 +18284,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="318">
+    <row r="318" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>1148</v>
       </c>
@@ -18281,7 +18304,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="319">
+    <row r="319" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>1148</v>
       </c>
@@ -18301,7 +18324,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="320">
+    <row r="320" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>1148</v>
       </c>
@@ -18321,7 +18344,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="321">
+    <row r="321" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>1148</v>
       </c>
@@ -18341,7 +18364,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="322">
+    <row r="322" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>1148</v>
       </c>
@@ -18361,7 +18384,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="323">
+    <row r="323" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>1148</v>
       </c>
@@ -18381,7 +18404,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="324">
+    <row r="324" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>1148</v>
       </c>
@@ -18401,7 +18424,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="325">
+    <row r="325" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>1148</v>
       </c>
@@ -18421,7 +18444,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="326">
+    <row r="326" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>1149</v>
       </c>
@@ -18442,9 +18465,10 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F326"/>
+  <autoFilter ref="A1:F326" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F326"/>
+    <ignoredError sqref="A1:F326" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>